--- a/data.mn/public/datasets/temperature-extremes-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/temperature-extremes-ulaanbaatar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C773"/>
+  <dimension ref="A1:C776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12018,6 +12018,51 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Maximum</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
